--- a/migration/workspace/reports/reconciliation_01_15_sep_partial.xlsx
+++ b/migration/workspace/reports/reconciliation_01_15_sep_partial.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>In Global Master v5</t>
+          <t>In Global Master v6</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -54232,7 +54232,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>In Global Master v5</t>
+          <t>In Global Master v6</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -60847,7 +60847,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>In Global Master v5</t>
+          <t>In Global Master v6</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -77926,7 +77926,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>PCS</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="D365" t="n">
@@ -77948,7 +77948,7 @@
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>unit mismatch: raw='GR' vs Global Base='PCS' and no approved conversion or valid physical-unit conversion exists -- NOT normalized (do not guess)</t>
+          <t>already in base unit</t>
         </is>
       </c>
       <c r="L365" t="b">
@@ -77973,7 +77973,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>PCS</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="D366" t="n">
@@ -77995,7 +77995,7 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>unit mismatch: raw='GR' vs Global Base='PCS' and no approved conversion or valid physical-unit conversion exists -- NOT normalized (do not guess)</t>
+          <t>already in base unit</t>
         </is>
       </c>
       <c r="L366" t="b">
